--- a/eclipse-workspace/proyectoMavenDAM2A25_26/src/main/resources/ejercicios_Excel_POI/vehiculosElectricos.xlsx
+++ b/eclipse-workspace/proyectoMavenDAM2A25_26/src/main/resources/ejercicios_Excel_POI/vehiculosElectricos.xlsx
@@ -3,17 +3,18 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{576BFE36-F5BC-4209-BBE9-10CAA2D8ADDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{CE3F24CC-7AEE-424A-AA0C-0C59126C2D7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="855" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="855" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet" sheetId="1" r:id="rId1"/>
     <sheet name="salamanca" sheetId="2" r:id="rId2"/>
     <sheet name="valladolid" sheetId="3" r:id="rId3"/>
+    <sheet name="zamora" r:id="rId9" sheetId="4"/>
   </sheets>
   <calcPr calcId="0"/>
-  <oleSize ref="A1"/>
+  <oleSize ref="A1:U22"/>
   <extLst>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1510" uniqueCount="716">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1567" uniqueCount="717">
   <si>
     <t>Nombre</t>
   </si>
@@ -2174,12 +2175,16 @@
   </si>
   <si>
     <t>EasyChargerEasyCharger</t>
+  </si>
+  <si>
+    <t>EasyCharger</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -2441,11 +2446,11 @@
   <dimension ref="A1:Z1000"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="39.140625" customWidth="1"/>
-    <col min="2" max="2" width="61.85546875" customWidth="1"/>
-    <col min="3" max="3" width="89.7109375" customWidth="1"/>
-    <col min="4" max="4" width="39.28515625" customWidth="1"/>
-    <col min="5" max="26" width="10.7109375" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="39.140625"/>
+    <col min="2" max="2" customWidth="true" width="89.0"/>
+    <col min="3" max="3" customWidth="true" width="89.7109375"/>
+    <col min="4" max="4" customWidth="true" width="39.28515625"/>
+    <col min="5" max="26" customWidth="true" width="10.7109375"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2521,7 +2526,7 @@
         <v>15</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>16</v>
@@ -2544,7 +2549,7 @@
         <v>21</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>22</v>
@@ -2567,7 +2572,7 @@
         <v>27</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>16</v>
@@ -2590,7 +2595,7 @@
         <v>31</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>32</v>
@@ -2656,7 +2661,7 @@
         <v>48</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>49</v>
@@ -2702,7 +2707,7 @@
         <v>57</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>16</v>
@@ -2748,7 +2753,7 @@
         <v>65</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>16</v>
@@ -2771,7 +2776,7 @@
         <v>69</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>70</v>
@@ -3254,7 +3259,7 @@
         <v>146</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>32</v>
@@ -3320,7 +3325,7 @@
         <v>158</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>32</v>
@@ -3659,7 +3664,7 @@
         <v>212</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>32</v>
@@ -4455,7 +4460,7 @@
         <v>312</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>32</v>
@@ -5159,7 +5164,7 @@
         <v>414</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="D119" s="2" t="s">
         <v>70</v>
@@ -5409,7 +5414,7 @@
         <v>458</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="D130" s="2" t="s">
         <v>32</v>
@@ -5961,7 +5966,7 @@
         <v>538</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="D154" s="2" t="s">
         <v>16</v>
@@ -6303,7 +6308,7 @@
         <v>601</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="D169" s="2" t="s">
         <v>10</v>
@@ -6464,7 +6469,7 @@
         <v>630</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="D176" s="2" t="s">
         <v>32</v>
@@ -6556,7 +6561,7 @@
         <v>646</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="D180" s="2" t="s">
         <v>32</v>
@@ -6671,7 +6676,7 @@
         <v>667</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="D185" s="2" t="s">
         <v>32</v>
@@ -6694,7 +6699,7 @@
         <v>671</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="D186" s="2" t="s">
         <v>32</v>
@@ -6970,7 +6975,7 @@
         <v>712</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="D198" s="2" t="s">
         <v>32</v>
@@ -7799,114 +7804,114 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+      <c r="A1" t="s" s="0">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" t="s" s="0">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>87</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>88</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>93</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>94</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="A4" t="s" s="0">
         <v>179</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" t="s" s="0">
         <v>180</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="A5" t="s" s="0">
         <v>490</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" t="s" s="0">
         <v>491</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="A6" t="s" s="0">
         <v>528</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" t="s" s="0">
         <v>529</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="A7" t="s" s="0">
         <v>532</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" t="s" s="0">
         <v>533</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="A8" t="s" s="0">
         <v>541</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" t="s" s="0">
         <v>542</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="A9" t="s" s="0">
         <v>554</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" t="s" s="0">
         <v>555</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="A10" t="s" s="0">
         <v>571</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" t="s" s="0">
         <v>572</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="A11" t="s" s="0">
         <v>579</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" t="s" s="0">
         <v>580</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="A12" t="s" s="0">
         <v>591</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" t="s" s="0">
         <v>592</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+      <c r="A13" t="s" s="0">
         <v>633</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" t="s" s="0">
         <v>634</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+      <c r="A14" t="s" s="0">
         <v>658</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" t="s" s="0">
         <v>659</v>
       </c>
     </row>
@@ -7921,438 +7926,520 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+      <c r="A1" t="s" s="0">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" t="s" s="0">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>30</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="A4" t="s" s="0">
         <v>131</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" t="s" s="0">
         <v>132</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="A5" t="s" s="0">
         <v>131</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" t="s" s="0">
         <v>132</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="A6" t="s" s="0">
         <v>131</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" t="s" s="0">
         <v>132</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="A7" t="s" s="0">
         <v>137</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" t="s" s="0">
         <v>138</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="A8" t="s" s="0">
         <v>137</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" t="s" s="0">
         <v>138</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="A9" t="s" s="0">
         <v>141</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" t="s" s="0">
         <v>142</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="A10" t="s" s="0">
         <v>141</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" t="s" s="0">
         <v>142</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="A11" t="s" s="0">
         <v>215</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" t="s" s="0">
         <v>216</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="A12" t="s" s="0">
         <v>233</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" t="s" s="0">
         <v>234</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+      <c r="A13" t="s" s="0">
         <v>242</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" t="s" s="0">
         <v>243</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+      <c r="A14" t="s" s="0">
         <v>246</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" t="s" s="0">
         <v>247</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+      <c r="A15" t="s" s="0">
         <v>246</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" t="s" s="0">
         <v>247</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+      <c r="A16" t="s" s="0">
         <v>254</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" t="s" s="0">
         <v>255</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+      <c r="A17" t="s" s="0">
         <v>258</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" t="s" s="0">
         <v>255</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+      <c r="A18" t="s" s="0">
         <v>258</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" t="s" s="0">
         <v>255</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+      <c r="A19" t="s" s="0">
         <v>254</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" t="s" s="0">
         <v>255</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+      <c r="A20" t="s" s="0">
         <v>261</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" t="s" s="0">
         <v>262</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+      <c r="A21" t="s" s="0">
         <v>265</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" t="s" s="0">
         <v>262</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+      <c r="A22" t="s" s="0">
         <v>261</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" t="s" s="0">
         <v>262</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+      <c r="A23" t="s" s="0">
         <v>265</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" t="s" s="0">
         <v>262</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+      <c r="A24" t="s" s="0">
         <v>277</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" t="s" s="0">
         <v>278</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+      <c r="A25" t="s" s="0">
         <v>288</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" t="s" s="0">
         <v>289</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+      <c r="A26" t="s" s="0">
         <v>288</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" t="s" s="0">
         <v>289</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+      <c r="A27" t="s" s="0">
         <v>300</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" t="s" s="0">
         <v>301</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
+      <c r="A28" t="s" s="0">
         <v>304</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" t="s" s="0">
         <v>301</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
+      <c r="A29" t="s" s="0">
         <v>307</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" t="s" s="0">
         <v>308</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
+      <c r="A30" t="s" s="0">
         <v>307</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" t="s" s="0">
         <v>308</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
+      <c r="A31" t="s" s="0">
         <v>319</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" t="s" s="0">
         <v>320</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
+      <c r="A32" t="s" s="0">
         <v>324</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" t="s" s="0">
         <v>325</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
+      <c r="A33" t="s" s="0">
         <v>324</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" t="s" s="0">
         <v>325</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
+      <c r="A34" t="s" s="0">
         <v>328</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" t="s" s="0">
         <v>329</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
+      <c r="A35" t="s" s="0">
         <v>328</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" t="s" s="0">
         <v>329</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
+      <c r="A36" t="s" s="0">
         <v>332</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" t="s" s="0">
         <v>333</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
+      <c r="A37" t="s" s="0">
         <v>332</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" t="s" s="0">
         <v>333</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
+      <c r="A38" t="s" s="0">
         <v>336</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" t="s" s="0">
         <v>337</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
+      <c r="A39" t="s" s="0">
         <v>340</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" t="s" s="0">
         <v>341</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
+      <c r="A40" t="s" s="0">
         <v>340</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B40" t="s" s="0">
         <v>341</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
+      <c r="A41" t="s" s="0">
         <v>352</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B41" t="s" s="0">
         <v>353</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
+      <c r="A42" t="s" s="0">
         <v>352</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B42" t="s" s="0">
         <v>353</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
+      <c r="A43" t="s" s="0">
         <v>392</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B43" t="s" s="0">
         <v>393</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
+      <c r="A44" t="s" s="0">
         <v>408</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B44" t="s" s="0">
         <v>409</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
+      <c r="A45" t="s" s="0">
         <v>413</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B45" t="s" s="0">
         <v>414</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
+      <c r="A46" t="s" s="0">
         <v>417</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B46" t="s" s="0">
         <v>418</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
+      <c r="A47" t="s" s="0">
         <v>501</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B47" t="s" s="0">
         <v>502</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
+      <c r="A48" t="s" s="0">
         <v>505</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B48" t="s" s="0">
         <v>502</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
+      <c r="A49" t="s" s="0">
         <v>596</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B49" t="s" s="0">
         <v>597</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
+      <c r="A50" t="s" s="0">
         <v>600</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B50" t="s" s="0">
         <v>601</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
+      <c r="A51" t="s" s="0">
         <v>704</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B51" t="s" s="0">
         <v>705</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
+      <c r="A52" t="s" s="0">
         <v>708</v>
       </c>
-      <c r="B52" t="s">
+      <c r="B52" t="s" s="0">
         <v>705</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
+      <c r="A53" t="s" s="0">
         <v>704</v>
       </c>
-      <c r="B53" t="s">
+      <c r="B53" t="s" s="0">
         <v>705</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
+      <c r="A54" t="s" s="0">
         <v>708</v>
       </c>
-      <c r="B54" t="s">
+      <c r="B54" t="s" s="0">
         <v>705</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B9"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="0">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>83</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>425</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>474</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>567</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>608</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>674</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>675</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
 </file>